--- a/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8677" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8677" uniqueCount="740">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -867,7 +867,7 @@
     <t>Code d'interprétation</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260716085852</t>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDAObservationInterpretation|2.0.3-sd</t>
   </si>
   <si>
     <t>Observation.methodCode</t>
@@ -2056,9 +2056,6 @@
   </si>
   <si>
     <t>Observation.entryRelationship.observation.referenceRange.observationRange.interpretationCode</t>
-  </si>
-  <si>
-    <t>http://hl7.org/cda/stds/core/ValueSet/CDAObservationInterpretation|2.0.3-sd</t>
   </si>
   <si>
     <t>ObservationRange.interpretationCode</t>
@@ -2646,7 +2643,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="80.01171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="68.65234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -26041,25 +26038,25 @@
       </c>
       <c r="Y232" s="2"/>
       <c r="Z232" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AA232" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB232" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC232" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD232" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE232" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF232" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="AA232" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB232" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC232" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD232" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE232" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF232" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -26079,10 +26076,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B233" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="B233" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -26180,10 +26177,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="B234" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="B234" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -26224,7 +26221,7 @@
         <v>75</v>
       </c>
       <c r="S234" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="T234" t="s" s="2">
         <v>75</v>
@@ -26283,10 +26280,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="B235" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="B235" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -26327,7 +26324,7 @@
         <v>75</v>
       </c>
       <c r="S235" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="T235" t="s" s="2">
         <v>75</v>
@@ -26386,10 +26383,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="B236" t="s" s="2">
         <v>671</v>
-      </c>
-      <c r="B236" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -26489,10 +26486,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="B237" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="B237" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -26592,10 +26589,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="B238" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="B238" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -26695,10 +26692,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="B239" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="B239" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -26796,10 +26793,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="B240" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="B240" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -26897,10 +26894,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="B241" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="B241" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -27000,10 +26997,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="B242" t="s" s="2">
         <v>683</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>684</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -27103,10 +27100,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="B243" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="B243" t="s" s="2">
-        <v>686</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -27206,10 +27203,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="B244" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="B244" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -27236,7 +27233,7 @@
       </c>
       <c r="L244" s="2"/>
       <c r="M244" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N244" s="2"/>
       <c r="O244" s="2"/>
@@ -27287,7 +27284,7 @@
         <v>75</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>81</v>
@@ -27307,10 +27304,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="B245" t="s" s="2">
         <v>691</v>
-      </c>
-      <c r="B245" t="s" s="2">
-        <v>692</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -27408,10 +27405,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="B246" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="B246" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -27509,10 +27506,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="B247" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="B247" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -27610,10 +27607,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="B248" t="s" s="2">
         <v>697</v>
-      </c>
-      <c r="B248" t="s" s="2">
-        <v>698</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -27711,10 +27708,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="B249" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="B249" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -27814,10 +27811,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="B250" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="B250" t="s" s="2">
-        <v>702</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -27917,10 +27914,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="B251" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="B251" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -28020,10 +28017,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="B252" t="s" s="2">
         <v>705</v>
-      </c>
-      <c r="B252" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -28123,10 +28120,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="B253" t="s" s="2">
         <v>707</v>
-      </c>
-      <c r="B253" t="s" s="2">
-        <v>708</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -28224,10 +28221,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="B254" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="B254" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -28261,7 +28258,7 @@
       </c>
       <c r="Q254" s="2"/>
       <c r="R254" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="S254" t="s" s="2">
         <v>75</v>
@@ -28301,7 +28298,7 @@
         <v>75</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>81</v>
@@ -28321,10 +28318,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="B255" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="B255" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -28351,7 +28348,7 @@
       </c>
       <c r="L255" s="2"/>
       <c r="M255" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="N255" s="2"/>
       <c r="O255" s="2"/>
@@ -28382,25 +28379,25 @@
       </c>
       <c r="Y255" s="2"/>
       <c r="Z255" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AA255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF255" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="AA255" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB255" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC255" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD255" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE255" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF255" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>76</v>
@@ -28420,10 +28417,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="B256" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="B256" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -28446,7 +28443,7 @@
         <v>75</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="L256" s="2"/>
       <c r="M256" s="2"/>
@@ -28499,7 +28496,7 @@
         <v>75</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>76</v>
@@ -28519,10 +28516,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="B257" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="B257" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -28545,7 +28542,7 @@
         <v>75</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="L257" s="2"/>
       <c r="M257" s="2"/>
@@ -28598,7 +28595,7 @@
         <v>75</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>81</v>
@@ -28618,7 +28615,7 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>360</v>
@@ -28717,7 +28714,7 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>364</v>
@@ -28816,7 +28813,7 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>368</v>
@@ -28915,7 +28912,7 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>372</v>
@@ -29014,7 +29011,7 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>376</v>
@@ -29113,7 +29110,7 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>380</v>
@@ -29610,10 +29607,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -29711,10 +29708,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -29812,10 +29809,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -29913,10 +29910,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -30014,10 +30011,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -30117,10 +30114,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -30220,10 +30217,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -30323,10 +30320,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -30426,10 +30423,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -30723,10 +30720,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -30749,7 +30746,7 @@
         <v>75</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="L279" s="2"/>
       <c r="M279" s="2"/>
@@ -30802,7 +30799,7 @@
         <v>75</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>81</v>

--- a/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -812,7 +812,7 @@
     <t>Niveau de complétude</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis|20260916095454</t>
   </si>
   <si>
     <t>Observation.effectiveTime</t>
@@ -876,7 +876,7 @@
     <t>Méthode ou technique employée</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-technique-biologie-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-technique-biologie-cisis|20260916095454</t>
   </si>
   <si>
     <t>Observation.targetSiteCode</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -951,7 +951,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">value:typeCode}
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
